--- a/docs/build/lakeshore-enterprise-context/source/08_operations_business_process/process_kpi_baseline.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/08_operations_business_process/process_kpi_baseline.xlsx
@@ -483,11 +483,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.8</v>
+        <v>21.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>82.1%</t>
         </is>
       </c>
     </row>
@@ -499,15 +499,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P2P</t>
+          <t>R2R</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.9</v>
+        <v>11.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>73.6%</t>
         </is>
       </c>
     </row>
@@ -519,15 +519,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>O2C</t>
+          <t>R2R</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>71.3%</t>
         </is>
       </c>
     </row>
@@ -543,11 +543,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.9</v>
+        <v>17.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>91.8%</t>
         </is>
       </c>
     </row>
@@ -563,11 +563,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.2</v>
+        <v>18.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>89.7%</t>
         </is>
       </c>
     </row>
@@ -579,15 +579,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>O2C</t>
+          <t>P2P</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.2</v>
+        <v>16.3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>87.1%</t>
         </is>
       </c>
     </row>
